--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.45478</v>
+        <v>16.82607</v>
       </c>
       <c r="D2" t="n">
-        <v>16.56012</v>
+        <v>16.62917</v>
       </c>
       <c r="E2" t="n">
-        <v>16.75402</v>
+        <v>16.73298</v>
       </c>
       <c r="F2" t="n">
-        <v>42.92166</v>
+        <v>41.65354</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04929</v>
+        <v>0.04916</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81143</v>
+        <v>1.80895</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.39758</v>
+        <v>16.64336</v>
       </c>
       <c r="D3" t="n">
-        <v>16.52358</v>
+        <v>16.45111</v>
       </c>
       <c r="E3" t="n">
-        <v>16.41783</v>
+        <v>16.6433</v>
       </c>
       <c r="F3" t="n">
-        <v>41.77114</v>
+        <v>42.60583</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05124</v>
+        <v>0.05037</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81845</v>
+        <v>1.81368</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.48254</v>
+        <v>16.64346</v>
       </c>
       <c r="D4" t="n">
-        <v>16.65758</v>
+        <v>16.23807</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73169</v>
+        <v>16.51719</v>
       </c>
       <c r="F4" t="n">
-        <v>41.96602</v>
+        <v>42.01409</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04953</v>
+        <v>0.05067</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82308</v>
+        <v>1.85359</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.64971</v>
+        <v>16.72075</v>
       </c>
       <c r="D6" t="n">
-        <v>15.90187</v>
+        <v>15.87292</v>
       </c>
       <c r="E6" t="n">
-        <v>16.43377</v>
+        <v>16.46471</v>
       </c>
       <c r="F6" t="n">
-        <v>21.68916</v>
+        <v>21.8744</v>
       </c>
       <c r="G6" t="n">
-        <v>33.91328</v>
+        <v>33.75168</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.50298</v>
+        <v>16.65258</v>
       </c>
       <c r="D7" t="n">
-        <v>16.02677</v>
+        <v>15.96909</v>
       </c>
       <c r="E7" t="n">
-        <v>16.17194</v>
+        <v>16.58671</v>
       </c>
       <c r="F7" t="n">
-        <v>21.6591</v>
+        <v>21.67991</v>
       </c>
       <c r="G7" t="n">
-        <v>34.24137</v>
+        <v>33.63699</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.3464</v>
+        <v>16.65883</v>
       </c>
       <c r="D8" t="n">
-        <v>16.05636</v>
+        <v>16.23435</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2058</v>
+        <v>16.35761</v>
       </c>
       <c r="F8" t="n">
-        <v>21.18765</v>
+        <v>21.69169</v>
       </c>
       <c r="G8" t="n">
-        <v>34.21147</v>
+        <v>33.87657</v>
       </c>
     </row>
   </sheetData>
